--- a/Expertly_ToDo_List.xlsx
+++ b/Expertly_ToDo_List.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="11_0463A05ADFE5BE30D7AA637DF86CD755EE4EC5D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07FCE5C9-8274-422C-AC8C-D6C519F97342}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5760" yWindow="3540" windowWidth="17280" windowHeight="9420" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Expertly To-Do List" sheetId="1" r:id="rId1"/>
